--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E96" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Die For Me</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>KONNAKOL</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:00</v>
+        <v>2:43</v>
       </c>
       <c r="H2" t="str">
-        <v>ZAYN</v>
+        <v>Perrie</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L2" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Two Six</v>
+        <v>Die For Me</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-09</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>The Fall-Off</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G3" t="str">
-        <v>3:16</v>
+        <v>3:00</v>
       </c>
       <c r="H3" t="str">
-        <v>J. Cole</v>
+        <v>ZAYN</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L3" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Two Six</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-09</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G4" t="str">
-        <v>3:29</v>
+        <v>3:16</v>
       </c>
       <c r="H4" t="str">
-        <v>Tame Impala</v>
+        <v>J. Cole</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L4" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Hotel California</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-09</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Piss In The Wind</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>2:08</v>
+        <v>3:29</v>
       </c>
       <c r="H5" t="str">
-        <v>Joji</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L5" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Homewrecker</v>
+        <v>Hotel California</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-09</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G6" t="str">
-        <v>3:29</v>
+        <v>2:08</v>
       </c>
       <c r="H6" t="str">
-        <v>sombr</v>
+        <v>Joji</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L6" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Might Just</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-09</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:43</v>
+        <v>3:29</v>
       </c>
       <c r="H7" t="str">
-        <v>Ella Mai</v>
+        <v>sombr</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L7" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Cloud 9</v>
+        <v>Might Just</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-09</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Cloud 9</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G8" t="str">
-        <v>3:33</v>
+        <v>3:43</v>
       </c>
       <c r="H8" t="str">
-        <v>Megan Moroney</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L8" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cry</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-09</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G9" t="str">
-        <v>3:07</v>
+        <v>3:33</v>
       </c>
       <c r="H9" t="str">
-        <v>Charlie Puth</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L9" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>I'll Change for You</v>
+        <v>Cry</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-09</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G10" t="str">
-        <v>3:16</v>
+        <v>3:07</v>
       </c>
       <c r="H10" t="str">
-        <v>Mitski</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L10" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ASSIGNMENT</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-09</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G11" t="str">
-        <v>2:23</v>
+        <v>3:16</v>
       </c>
       <c r="H11" t="str">
-        <v>Power Snatch</v>
+        <v>Mitski</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L11" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Como en el Idilio</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-09</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>4:27</v>
+        <v>2:23</v>
       </c>
       <c r="H12" t="str">
-        <v>Marc Anthony</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L12" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>golden boy</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-09</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>stardust - EP</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:17</v>
+        <v>4:27</v>
       </c>
       <c r="H13" t="str">
-        <v>Freya Skye</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L13" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-09</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G14" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H14" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L14" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-09</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G15" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H15" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L15" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Adrenaline</v>
+        <v>Heaven</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-09</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G16" t="str">
-        <v>3:39</v>
+        <v>4:26</v>
       </c>
       <c r="H16" t="str">
-        <v>ATEEZ</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L16" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sweet To Me</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-09</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Sunday Best</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G17" t="str">
-        <v>4:17</v>
+        <v>3:39</v>
       </c>
       <c r="H17" t="str">
-        <v>Nick Jonas</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L17" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Time Goes On</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-09</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G18" t="str">
-        <v>2:55</v>
+        <v>4:17</v>
       </c>
       <c r="H18" t="str">
-        <v>Koe Wetzel</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L18" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drive Safe</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-09</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>Myles Smith</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L19" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Love To Be Loved</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-09</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:21</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L20" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-09</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:02</v>
+        <v>2:50</v>
       </c>
       <c r="H21" t="str">
-        <v>Eden Muñoz</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L21" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Omens</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-09</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Omens - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:00</v>
+        <v>3:02</v>
       </c>
       <c r="H22" t="str">
-        <v>EsDeeKid</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L22" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>My Regards</v>
+        <v>Omens</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-09</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Florescence</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:11</v>
+        <v>2:00</v>
       </c>
       <c r="H23" t="str">
-        <v>Maisie Peters</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L23" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Time After Time</v>
+        <v>My Regards</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-09</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Time After Time - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G24" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H24" t="str">
-        <v>EJAE</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L24" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Time After Time</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-09</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>ODYSSEY</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H25" t="str">
-        <v>ILLENIUM</v>
+        <v>EJAE</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L25" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-09</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>3:12</v>
       </c>
       <c r="H26" t="str">
-        <v>Pitbull</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L26" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Plei</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-09</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Plei - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Chuwi</v>
+        <v>Pitbull</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L27" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Plei</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-09</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H28" t="str">
-        <v>Dua Saleh</v>
+        <v>Chuwi</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L28" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Rain</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-09</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Rain - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G29" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>FISHER</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L29" t="str">
-        <v>Rain - FISHER</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Release The Pressure</v>
+        <v>Rain</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-09</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H30" t="str">
-        <v>Calvin Harris</v>
+        <v>FISHER</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L30" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-09</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H31" t="str">
-        <v>Robyn</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L31" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>heal something</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-09</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>ACT II</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:01</v>
+        <v>3:44</v>
       </c>
       <c r="H32" t="str">
-        <v>Sasha Keable</v>
+        <v>Robyn</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L32" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Buenos Días</v>
+        <v>heal something</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-09</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Buenos Días - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G33" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H33" t="str">
-        <v>Eladio Carrión</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L33" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>COOK</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-09</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>COOK - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H34" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L34" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>You Got to Lose</v>
+        <v>COOK</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-09</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Peaches!</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H35" t="str">
-        <v>The Black Keys</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L35" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Different Kind Of Love</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-09</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G36" t="str">
-        <v>3:39</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L36" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Living Water</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-09</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G37" t="str">
-        <v>2:09</v>
+        <v>3:39</v>
       </c>
       <c r="H37" t="str">
-        <v>Lecrae</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L37" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>What It Feels Like</v>
+        <v>Living Water</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-09</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G38" t="str">
-        <v>2:18</v>
+        <v>2:09</v>
       </c>
       <c r="H38" t="str">
-        <v>Dillon Francis</v>
+        <v>Lecrae</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L38" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>neck</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-09</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>neck - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:40</v>
+        <v>2:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Mau P</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L39" t="str">
-        <v>neck - Mau P</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Colorblind</v>
+        <v>neck</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-09</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Colorblind - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:56</v>
+        <v>3:40</v>
       </c>
       <c r="H40" t="str">
-        <v>Gavin Adcock</v>
+        <v>Mau P</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L40" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Colorblind</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-09</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Tenterhooks</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H41" t="str">
-        <v>Silversun Pickups</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L41" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Flavorless</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-09</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Flavorless - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G42" t="str">
-        <v>3:31</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L42" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nunca</v>
+        <v>Flavorless</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-09</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>ESCENAS</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:05</v>
+        <v>3:31</v>
       </c>
       <c r="H43" t="str">
-        <v>Sin Bandera</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L43" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Just In Case</v>
+        <v>Nunca</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-09</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G44" t="str">
-        <v>1:45</v>
+        <v>3:05</v>
       </c>
       <c r="H44" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L44" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Thinking of You</v>
+        <v>Just In Case</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-09</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Thinking of You - Single</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G45" t="str">
-        <v>3:00</v>
+        <v>1:45</v>
       </c>
       <c r="H45" t="str">
-        <v>AP Dhillon</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L45" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>House Of Cards</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-09</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>House of Cards</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:26</v>
+        <v>3:00</v>
       </c>
       <c r="H46" t="str">
-        <v>The Amity Affliction</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L46" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Stay With Me</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-09</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Stay With Me - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G47" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H47" t="str">
-        <v>Agents Of Time</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L47" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>I had a dream...</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-09</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:39</v>
+        <v>3:21</v>
       </c>
       <c r="H48" t="str">
-        <v>R3HAB</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L48" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Back to You</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-09</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Satellite</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G49" t="str">
-        <v>3:10</v>
+        <v>2:39</v>
       </c>
       <c r="H49" t="str">
-        <v>Charlotte Sands</v>
+        <v>R3HAB</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L49" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>rager</v>
+        <v>Back to You</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-09</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>rager</v>
+        <v>Satellite</v>
       </c>
       <c r="G50" t="str">
-        <v>2:48</v>
+        <v>3:10</v>
       </c>
       <c r="H50" t="str">
-        <v>Blusher</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L50" t="str">
-        <v>rager - Blusher</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>If Only</v>
+        <v>rager</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-09</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Patchwork</v>
+        <v>rager</v>
       </c>
       <c r="G51" t="str">
-        <v>3:28</v>
+        <v>2:48</v>
       </c>
       <c r="H51" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Blusher</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L51" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>If Only</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-09</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H52" t="str">
-        <v>Omah Lay</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L52" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-09</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Sweet Nothings</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:32</v>
+        <v>3:01</v>
       </c>
       <c r="H53" t="str">
-        <v>Jaymin</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L53" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>you woke me up</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-09</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>you woke me up - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G54" t="str">
-        <v>3:14</v>
+        <v>2:32</v>
       </c>
       <c r="H54" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Jaymin</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L54" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No One’s Business</v>
+        <v>you woke me up</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-09</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>No One’s Business - Single</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:00</v>
+        <v>3:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Alicia Creti</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L55" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-09</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:13</v>
+        <v>3:00</v>
       </c>
       <c r="H56" t="str">
-        <v>Bryant Barnes</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L56" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>TWICE</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-09</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>KINDA HARD</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G57" t="str">
-        <v>3:44</v>
+        <v>3:13</v>
       </c>
       <c r="H57" t="str">
-        <v>Bilmuri</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L57" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ROOFTOP</v>
+        <v>TWICE</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-09</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G58" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H58" t="str">
-        <v>Hulvey</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L58" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louisiana Rain</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-09</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:41</v>
+        <v>3:22</v>
       </c>
       <c r="H59" t="str">
-        <v>Hunter Plake</v>
+        <v>Hulvey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L59" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-09</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>1:55</v>
+        <v>3:41</v>
       </c>
       <c r="H60" t="str">
-        <v>Zoe Levert</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L60" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-09</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>1:55</v>
       </c>
       <c r="H61" t="str">
-        <v>Cole Knight</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L61" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-09</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>6:54</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L62" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-09</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Liturgy of Death</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:56</v>
+        <v>6:54</v>
       </c>
       <c r="H63" t="str">
-        <v>Mayhem</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L63" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BLEACH</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-09</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>BLEACH - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G64" t="str">
-        <v>2:28</v>
+        <v>4:56</v>
       </c>
       <c r="H64" t="str">
-        <v>Ecca Vandal</v>
+        <v>Mayhem</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L64" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>pretty in pink</v>
+        <v>BLEACH</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-09</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>AngelPink</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H65" t="str">
-        <v>Keni Titus</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L65" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Pickup Man</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-09</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Pickup Man - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G66" t="str">
-        <v>3:28</v>
+        <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L66" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-09</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:48</v>
+        <v>3:28</v>
       </c>
       <c r="H67" t="str">
-        <v>Zach John King</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L67" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Roses</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-09</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>The Roses - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:02</v>
+        <v>2:48</v>
       </c>
       <c r="H68" t="str">
-        <v>Russell Dickerson</v>
+        <v>Zach John King</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L68" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>I Should Know Better</v>
+        <v>The Roses</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-09</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Under The Streetlights</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H69" t="str">
-        <v>Michael Marcagi</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L69" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Never Do</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-09</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Never Do - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G70" t="str">
-        <v>1:58</v>
+        <v>3:33</v>
       </c>
       <c r="H70" t="str">
-        <v>charlieonnafriday</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L70" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Primary Colors</v>
+        <v>Never Do</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-09</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Lost on You</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:37</v>
+        <v>1:58</v>
       </c>
       <c r="H71" t="str">
-        <v>Tigers Jaw</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L71" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Rock Bottom</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-09</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G72" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H72" t="str">
-        <v>King Krule</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L72" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Te Dedico</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-09</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:45</v>
+        <v>4:10</v>
       </c>
       <c r="H73" t="str">
-        <v>Carlos Vives</v>
+        <v>King Krule</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L73" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-09</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>18</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:38</v>
+        <v>3:45</v>
       </c>
       <c r="H74" t="str">
-        <v>Conexión Divina</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L74" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>I Dare You</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-09</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>I Dare You - Single</v>
+        <v>18</v>
       </c>
       <c r="G75" t="str">
-        <v>3:25</v>
+        <v>2:38</v>
       </c>
       <c r="H75" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L75" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>new irish boyfriend</v>
+        <v>I Dare You</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-09</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>long time caller, first time listener</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H76" t="str">
-        <v>vegas water taxi</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L76" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-09</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Singing</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G77" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H77" t="str">
-        <v>Gia Margaret</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L77" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-09</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Big Changes</v>
+        <v>Singing</v>
       </c>
       <c r="G78" t="str">
-        <v>6:05</v>
+        <v>3:05</v>
       </c>
       <c r="H78" t="str">
-        <v>Status/Non-Status</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L78" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-09</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Big Changes</v>
       </c>
       <c r="G79" t="str">
-        <v>4:09</v>
+        <v>6:05</v>
       </c>
       <c r="H79" t="str">
-        <v>Julian Lage</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L79" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Big Deal</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-09</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Big Deal - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G80" t="str">
-        <v>3:47</v>
+        <v>4:09</v>
       </c>
       <c r="H80" t="str">
-        <v>In Color</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L80" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Buy What U Want</v>
+        <v>Big Deal</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-09</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G81" t="str">
         <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>Black Fortune</v>
+        <v>In Color</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L81" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Common Ground</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-09</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Common Ground - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G82" t="str">
-        <v>1:42</v>
+        <v>3:47</v>
       </c>
       <c r="H82" t="str">
-        <v>ELIO</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L82" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Cellophane</v>
+        <v>Common Ground</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-09</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Cellophane - Single</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>4:21</v>
+        <v>1:42</v>
       </c>
       <c r="H83" t="str">
-        <v>Maddie Zahm</v>
+        <v>ELIO</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L83" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>96 Camry</v>
+        <v>Cellophane</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-09</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:15</v>
+        <v>4:21</v>
       </c>
       <c r="H84" t="str">
-        <v>RAAHiiM</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L84" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>La Allstar</v>
+        <v>96 Camry</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-09</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>La Allstar - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G85" t="str">
-        <v>2:49</v>
+        <v>3:15</v>
       </c>
       <c r="H85" t="str">
-        <v>ELIKAI</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L85" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Luka</v>
+        <v>La Allstar</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-09</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Luka - Single</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:07</v>
+        <v>2:49</v>
       </c>
       <c r="H86" t="str">
-        <v>Fonta</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L86" t="str">
-        <v>Luka - Fonta</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Luka</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-09</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:06</v>
+        <v>2:07</v>
       </c>
       <c r="H87" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Fonta</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L87" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>In My Blue</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-09</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Rosie Carney</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L88" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>In My Blue</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-09</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G89" t="str">
-        <v>3:20</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L89" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Silently</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-09</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Croak Dream</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G90" t="str">
-        <v>3:29</v>
+        <v>3:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Puma Blue</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L90" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Silently</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-09</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G91" t="str">
-        <v>3:05</v>
+        <v>3:29</v>
       </c>
       <c r="H91" t="str">
-        <v>Anna Graves</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L91" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Tormentor</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-09</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:40</v>
+        <v>3:05</v>
       </c>
       <c r="H92" t="str">
-        <v>Ninush</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L92" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Red Rocking Chair</v>
+        <v>Tormentor</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-09</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G93" t="str">
-        <v>6:28</v>
+        <v>2:40</v>
       </c>
       <c r="H93" t="str">
-        <v>All Them Witches</v>
+        <v>Ninush</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L93" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-09</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>...of Death and Fire</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>7:07</v>
+        <v>6:28</v>
       </c>
       <c r="H94" t="str">
-        <v>In Aeternum</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L94" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mizantrop</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-09</v>
@@ -3985,68 +3985,106 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Mizantrop</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G95" t="str">
-        <v>3:42</v>
+        <v>7:07</v>
       </c>
       <c r="H95" t="str">
-        <v>She Past Away</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L95" t="str">
-        <v>Mizantrop - She Past Away</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3:42</v>
+      </c>
+      <c r="H96" t="str">
+        <v>She Past Away</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Mizantrop - She Past Away</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>In the Name of the Moth</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
-      <c r="D96" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
+      <c r="D97" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>Hidden Fires Burn Hottest</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>7:15</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>Bosse-de-Nage</v>
       </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L97" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E97" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Woman In Love</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G2" t="str">
-        <v>2:43</v>
+        <v>4:03</v>
       </c>
       <c r="H2" t="str">
-        <v>Perrie</v>
+        <v>MUNA</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L2" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="3">
@@ -892,13 +892,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>golden boy</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-10</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>stardust - EP</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:17</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>Freya Skye</v>
+        <v>Perrie</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L14" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-10</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G15" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H15" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L15" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-10</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G16" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H16" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L16" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Adrenaline</v>
+        <v>Heaven</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-10</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G17" t="str">
-        <v>3:39</v>
+        <v>4:26</v>
       </c>
       <c r="H17" t="str">
-        <v>ATEEZ</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L17" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sweet To Me</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-10</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Sunday Best</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G18" t="str">
-        <v>4:17</v>
+        <v>3:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Nick Jonas</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L18" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Time Goes On</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-10</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>4:17</v>
       </c>
       <c r="H19" t="str">
-        <v>Koe Wetzel</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L19" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Drive Safe</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-10</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Myles Smith</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L20" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Love To Be Loved</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-10</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:50</v>
+        <v>3:21</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L21" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-10</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:02</v>
+        <v>2:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Eden Muñoz</v>
+        <v>The Warning</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L22" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Omens</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-10</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Omens - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:00</v>
+        <v>3:02</v>
       </c>
       <c r="H23" t="str">
-        <v>EsDeeKid</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L23" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>My Regards</v>
+        <v>Omens</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-10</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Florescence</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:11</v>
+        <v>2:00</v>
       </c>
       <c r="H24" t="str">
-        <v>Maisie Peters</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L24" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Time After Time</v>
+        <v>My Regards</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-10</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Time After Time - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G25" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H25" t="str">
-        <v>EJAE</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L25" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Time After Time</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-10</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>ODYSSEY</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H26" t="str">
-        <v>ILLENIUM</v>
+        <v>EJAE</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L26" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-10</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G27" t="str">
-        <v>3:37</v>
+        <v>3:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Pitbull</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L27" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plei</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-10</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Plei - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H28" t="str">
-        <v>Chuwi</v>
+        <v>Pitbull</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L28" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Plei</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-10</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H29" t="str">
-        <v>Dua Saleh</v>
+        <v>Chuwi</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L29" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Rain</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-10</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Rain - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G30" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H30" t="str">
-        <v>FISHER</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L30" t="str">
-        <v>Rain - FISHER</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Release The Pressure</v>
+        <v>Rain</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-10</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H31" t="str">
-        <v>Calvin Harris</v>
+        <v>FISHER</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L31" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-10</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H32" t="str">
-        <v>Robyn</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L32" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>heal something</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-10</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>ACT II</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:01</v>
+        <v>3:44</v>
       </c>
       <c r="H33" t="str">
-        <v>Sasha Keable</v>
+        <v>Robyn</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L33" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Buenos Días</v>
+        <v>heal something</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-10</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Buenos Días - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G34" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H34" t="str">
-        <v>Eladio Carrión</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L34" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>COOK</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-10</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>COOK - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L35" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>You Got to Lose</v>
+        <v>COOK</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-10</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Peaches!</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H36" t="str">
-        <v>The Black Keys</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L36" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Different Kind Of Love</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-10</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G37" t="str">
-        <v>3:39</v>
+        <v>3:17</v>
       </c>
       <c r="H37" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L37" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Living Water</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-10</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G38" t="str">
-        <v>2:09</v>
+        <v>3:39</v>
       </c>
       <c r="H38" t="str">
-        <v>Lecrae</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L38" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>What It Feels Like</v>
+        <v>Living Water</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-10</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G39" t="str">
-        <v>2:18</v>
+        <v>2:09</v>
       </c>
       <c r="H39" t="str">
-        <v>Dillon Francis</v>
+        <v>Lecrae</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L39" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>neck</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-10</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>neck - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:40</v>
+        <v>2:18</v>
       </c>
       <c r="H40" t="str">
-        <v>Mau P</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L40" t="str">
-        <v>neck - Mau P</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Colorblind</v>
+        <v>neck</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-10</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Colorblind - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:56</v>
+        <v>3:40</v>
       </c>
       <c r="H41" t="str">
-        <v>Gavin Adcock</v>
+        <v>Mau P</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L41" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Colorblind</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-10</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Tenterhooks</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H42" t="str">
-        <v>Silversun Pickups</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L42" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Flavorless</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-10</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Flavorless - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G43" t="str">
-        <v>3:31</v>
+        <v>3:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L43" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nunca</v>
+        <v>Flavorless</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-10</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>ESCENAS</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:05</v>
+        <v>3:31</v>
       </c>
       <c r="H44" t="str">
-        <v>Sin Bandera</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L44" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Just In Case</v>
+        <v>Nunca</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-10</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G45" t="str">
-        <v>1:45</v>
+        <v>3:05</v>
       </c>
       <c r="H45" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L45" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Thinking of You</v>
+        <v>Just In Case</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-10</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Thinking of You - Single</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G46" t="str">
-        <v>3:00</v>
+        <v>1:45</v>
       </c>
       <c r="H46" t="str">
-        <v>AP Dhillon</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L46" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>House Of Cards</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-10</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>House of Cards</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:26</v>
+        <v>3:00</v>
       </c>
       <c r="H47" t="str">
-        <v>The Amity Affliction</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L47" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Stay With Me</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-10</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Stay With Me - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G48" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Agents Of Time</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L48" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>I had a dream...</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-10</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:39</v>
+        <v>3:21</v>
       </c>
       <c r="H49" t="str">
-        <v>R3HAB</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L49" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Back to You</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-10</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Satellite</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G50" t="str">
-        <v>3:10</v>
+        <v>2:39</v>
       </c>
       <c r="H50" t="str">
-        <v>Charlotte Sands</v>
+        <v>R3HAB</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L50" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>rager</v>
+        <v>Back to You</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-10</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>rager</v>
+        <v>Satellite</v>
       </c>
       <c r="G51" t="str">
-        <v>2:48</v>
+        <v>3:10</v>
       </c>
       <c r="H51" t="str">
-        <v>Blusher</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L51" t="str">
-        <v>rager - Blusher</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>If Only</v>
+        <v>rager</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-10</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Patchwork</v>
+        <v>rager</v>
       </c>
       <c r="G52" t="str">
-        <v>3:28</v>
+        <v>2:48</v>
       </c>
       <c r="H52" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Blusher</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L52" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>If Only</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-10</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G53" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H53" t="str">
-        <v>Omah Lay</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L53" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-10</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Sweet Nothings</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:32</v>
+        <v>3:01</v>
       </c>
       <c r="H54" t="str">
-        <v>Jaymin</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L54" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>you woke me up</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-10</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>you woke me up - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G55" t="str">
-        <v>3:14</v>
+        <v>2:32</v>
       </c>
       <c r="H55" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Jaymin</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L55" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No One’s Business</v>
+        <v>you woke me up</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-10</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>No One’s Business - Single</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:00</v>
+        <v>3:14</v>
       </c>
       <c r="H56" t="str">
-        <v>Alicia Creti</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L56" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-10</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:13</v>
+        <v>3:00</v>
       </c>
       <c r="H57" t="str">
-        <v>Bryant Barnes</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L57" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TWICE</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-10</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>KINDA HARD</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G58" t="str">
-        <v>3:44</v>
+        <v>3:13</v>
       </c>
       <c r="H58" t="str">
-        <v>Bilmuri</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L58" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ROOFTOP</v>
+        <v>TWICE</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-10</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G59" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H59" t="str">
-        <v>Hulvey</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L59" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louisiana Rain</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-10</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:41</v>
+        <v>3:22</v>
       </c>
       <c r="H60" t="str">
-        <v>Hunter Plake</v>
+        <v>Hulvey</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L60" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-10</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>1:55</v>
+        <v>3:41</v>
       </c>
       <c r="H61" t="str">
-        <v>Zoe Levert</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L61" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-10</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>1:55</v>
       </c>
       <c r="H62" t="str">
-        <v>Cole Knight</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L62" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-10</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>6:54</v>
+        <v>3:21</v>
       </c>
       <c r="H63" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L63" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-10</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Liturgy of Death</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:56</v>
+        <v>6:54</v>
       </c>
       <c r="H64" t="str">
-        <v>Mayhem</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L64" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>BLEACH</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-10</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>BLEACH - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G65" t="str">
-        <v>2:28</v>
+        <v>4:56</v>
       </c>
       <c r="H65" t="str">
-        <v>Ecca Vandal</v>
+        <v>Mayhem</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L65" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>pretty in pink</v>
+        <v>BLEACH</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-10</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>AngelPink</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H66" t="str">
-        <v>Keni Titus</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L66" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Pickup Man</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-10</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Pickup Man - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G67" t="str">
-        <v>3:28</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L67" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-10</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:48</v>
+        <v>3:28</v>
       </c>
       <c r="H68" t="str">
-        <v>Zach John King</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L68" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Roses</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-10</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>The Roses - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:02</v>
+        <v>2:48</v>
       </c>
       <c r="H69" t="str">
-        <v>Russell Dickerson</v>
+        <v>Zach John King</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L69" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>I Should Know Better</v>
+        <v>The Roses</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-10</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Under The Streetlights</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H70" t="str">
-        <v>Michael Marcagi</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L70" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Never Do</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-10</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Never Do - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G71" t="str">
-        <v>1:58</v>
+        <v>3:33</v>
       </c>
       <c r="H71" t="str">
-        <v>charlieonnafriday</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L71" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Primary Colors</v>
+        <v>Never Do</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-10</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Lost on You</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:37</v>
+        <v>1:58</v>
       </c>
       <c r="H72" t="str">
-        <v>Tigers Jaw</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L72" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Rock Bottom</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-10</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G73" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H73" t="str">
-        <v>King Krule</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L73" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Te Dedico</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-10</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:45</v>
+        <v>4:10</v>
       </c>
       <c r="H74" t="str">
-        <v>Carlos Vives</v>
+        <v>King Krule</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L74" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-10</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>18</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:38</v>
+        <v>3:45</v>
       </c>
       <c r="H75" t="str">
-        <v>Conexión Divina</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L75" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>I Dare You</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-10</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>I Dare You - Single</v>
+        <v>18</v>
       </c>
       <c r="G76" t="str">
-        <v>3:25</v>
+        <v>2:38</v>
       </c>
       <c r="H76" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L76" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>new irish boyfriend</v>
+        <v>I Dare You</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-10</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>long time caller, first time listener</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H77" t="str">
-        <v>vegas water taxi</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L77" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-10</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Singing</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G78" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H78" t="str">
-        <v>Gia Margaret</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L78" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-10</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Big Changes</v>
+        <v>Singing</v>
       </c>
       <c r="G79" t="str">
-        <v>6:05</v>
+        <v>3:05</v>
       </c>
       <c r="H79" t="str">
-        <v>Status/Non-Status</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L79" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-10</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Big Changes</v>
       </c>
       <c r="G80" t="str">
-        <v>4:09</v>
+        <v>6:05</v>
       </c>
       <c r="H80" t="str">
-        <v>Julian Lage</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L80" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Big Deal</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-10</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Big Deal - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>4:09</v>
       </c>
       <c r="H81" t="str">
-        <v>In Color</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L81" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Buy What U Want</v>
+        <v>Big Deal</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-10</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G82" t="str">
         <v>3:47</v>
       </c>
       <c r="H82" t="str">
-        <v>Black Fortune</v>
+        <v>In Color</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L82" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Common Ground</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-10</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Common Ground - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G83" t="str">
-        <v>1:42</v>
+        <v>3:47</v>
       </c>
       <c r="H83" t="str">
-        <v>ELIO</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L83" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cellophane</v>
+        <v>Common Ground</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-10</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Cellophane - Single</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>4:21</v>
+        <v>1:42</v>
       </c>
       <c r="H84" t="str">
-        <v>Maddie Zahm</v>
+        <v>ELIO</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L84" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>96 Camry</v>
+        <v>Cellophane</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-10</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:15</v>
+        <v>4:21</v>
       </c>
       <c r="H85" t="str">
-        <v>RAAHiiM</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L85" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>La Allstar</v>
+        <v>96 Camry</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-10</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>La Allstar - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G86" t="str">
-        <v>2:49</v>
+        <v>3:15</v>
       </c>
       <c r="H86" t="str">
-        <v>ELIKAI</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L86" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Luka</v>
+        <v>La Allstar</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-10</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Luka - Single</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:07</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Fonta</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L87" t="str">
-        <v>Luka - Fonta</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Luka</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-10</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:06</v>
+        <v>2:07</v>
       </c>
       <c r="H88" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Fonta</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L88" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>In My Blue</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-10</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H89" t="str">
-        <v>Rosie Carney</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L89" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>In My Blue</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-10</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G90" t="str">
-        <v>3:20</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L90" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Silently</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-10</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Croak Dream</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G91" t="str">
-        <v>3:29</v>
+        <v>3:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Puma Blue</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L91" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Silently</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-10</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G92" t="str">
-        <v>3:05</v>
+        <v>3:29</v>
       </c>
       <c r="H92" t="str">
-        <v>Anna Graves</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L92" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tormentor</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-10</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:40</v>
+        <v>3:05</v>
       </c>
       <c r="H93" t="str">
-        <v>Ninush</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L93" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Red Rocking Chair</v>
+        <v>Tormentor</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-10</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G94" t="str">
-        <v>6:28</v>
+        <v>2:40</v>
       </c>
       <c r="H94" t="str">
-        <v>All Them Witches</v>
+        <v>Ninush</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L94" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-10</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>...of Death and Fire</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>7:07</v>
+        <v>6:28</v>
       </c>
       <c r="H95" t="str">
-        <v>In Aeternum</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L95" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Mizantrop</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-10</v>
@@ -4023,68 +4023,106 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Mizantrop</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G96" t="str">
-        <v>3:42</v>
+        <v>7:07</v>
       </c>
       <c r="H96" t="str">
-        <v>She Past Away</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L96" t="str">
-        <v>Mizantrop - She Past Away</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="G97" t="str">
+        <v>3:42</v>
+      </c>
+      <c r="H97" t="str">
+        <v>She Past Away</v>
+      </c>
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+      </c>
+      <c r="K97" t="str">
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Mizantrop - She Past Away</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>In the Name of the Moth</v>
       </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
-      <c r="D97" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
+      <c r="D98" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>Hidden Fires Burn Hottest</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G98" t="str">
         <v>7:15</v>
       </c>
-      <c r="H97" t="str">
+      <c r="H98" t="str">
         <v>Bosse-de-Nage</v>
       </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
         <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
-      <c r="L97" t="str">
+      <c r="L98" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E98" t="str">
         <v/>
